--- a/client/public/products/pack3-finance-cheat-sheets/wrap-rate-breakdown.xlsx
+++ b/client/public/products/pack3-finance-cheat-sheets/wrap-rate-breakdown.xlsx
@@ -774,7 +774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="2" customWidth="1" style="33" min="1" max="1"/>
@@ -811,6 +811,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="21.75" customHeight="1" s="34">
       <c r="B4" s="40" t="inlineStr">
         <is>
@@ -910,6 +911,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="21.75" customHeight="1" s="34">
       <c r="B12" s="46" t="inlineStr">
         <is>
@@ -1091,6 +1093,7 @@
         <v/>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="21.75" customHeight="1" s="34">
       <c r="B23" s="40" t="inlineStr">
         <is>
@@ -1130,6 +1133,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27" ht="15.75" customHeight="1" s="34">
       <c r="B27" s="44" t="inlineStr">
         <is>
@@ -1147,12 +1151,10 @@
     <row r="29">
       <c r="B29" s="33" t="inlineStr">
         <is>
-          <t>★ CMMC Compliance Costs (Emerging ODC/Pass-Through): CMMC Phase 1 self-assessments active Nov 10, 2025; Phase 2 C3PAO assessments mandatory by Nov 10, 2026. Budget $50K–$250K for C3PAO assessment fees and $25K–$100K/yr for continuous monitoring tools. Include as ODC pass-through or in G&amp;A pool per CAS/FAR 31.205 — coordinate with DCAA on cost allocation. (Source: CMMC Final Rule, 32 CFR Part 170, Oct 2024; FAC 2025-07)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31"/>
+          <t>★ CMMC Compliance Costs (Emerging ODC/Pass-Through): CMMC Phase 1 self-assessments active Nov 10, 2025; Phase 2 C3PAO assessments mandatory by Nov 10, 2026. Budget $50K–$250K for C3PAO assessment fees and $25K–$100K/yr for continuous monitoring tools. Include as ODC pass-through or in G&amp;A pool per CAS/FAR 31.205 — coordinate with DCAA on cost allocation. (Source: CMMC Final Rule, 32 CFR Part 170, Oct 2024; FAC 2025-06)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="D25:E25"/>
@@ -1179,7 +1181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="2" customWidth="1" style="33" min="1" max="1"/>
@@ -1211,6 +1213,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="27.75" customHeight="1" s="34">
       <c r="B4" s="55" t="inlineStr">
         <is>
@@ -1493,13 +1496,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CMMC COMPLIANCE COSTS (Emerging ODC/Pass-Through, FAC 2025-07): Phase 1 self-assessment active Nov 10, 2025; Phase 2 C3PAO required by Nov 10, 2026. C3PAO assessment fees: $50K–$250K. Continuous monitoring tools: $25K–$100K/yr. Factor into overhead/G&amp;A or propose as direct ODC pass-through. Cleared professional and cyber contractors should already be planning for this cost.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+      <c r="B14" s="33" t="inlineStr">
+        <is>
+          <t>CMMC COMPLIANCE COSTS (Emerging ODC/Pass-Through, FAC 2025-06): Phase 1 self-assessment active Nov 10, 2025; Phase 2 C3PAO required by Nov 10, 2026. C3PAO assessment fees: $50K–$250K. Continuous monitoring tools: $25K–$100K/yr. Factor into overhead/G&amp;A or propose as direct ODC pass-through. Cleared professional and cyber contractors should already be planning for this cost.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B13:H13"/>
@@ -1547,6 +1549,7 @@
       </c>
       <c r="D2" s="35" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="21.75" customHeight="1" s="34">
       <c r="B4" s="40" t="inlineStr">
         <is>
@@ -1606,6 +1609,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="21.75" customHeight="1" s="34">
       <c r="B14" s="40" t="inlineStr">
         <is>
@@ -1661,6 +1665,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="21.75" customHeight="1" s="34">
       <c r="B24" s="40" t="inlineStr">
         <is>
@@ -1751,6 +1756,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39" ht="21.75" customHeight="1" s="34">
       <c r="B39" s="40" t="inlineStr">
         <is>
@@ -1813,6 +1819,7 @@
         </is>
       </c>
     </row>
+    <row r="49"/>
     <row r="50" ht="21.75" customHeight="1" s="34">
       <c r="B50" s="40" t="inlineStr">
         <is>
@@ -1890,6 +1897,7 @@
         </is>
       </c>
     </row>
+    <row r="61"/>
     <row r="62" ht="15" customHeight="1" s="34">
       <c r="B62" s="54" t="inlineStr">
         <is>
